--- a/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt2_rubricas.xlsx
@@ -1800,13 +1800,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FC84876-0427-48DA-A2D2-3FEF9C4104B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4423BE5-3AC0-4397-A323-E910F19B36D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A482B2FA-C7B5-4F64-B40E-E1D94757EA30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C5D636A-DE3F-4843-8F58-9118E007D909}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7524E721-2A7B-428C-A0AB-9CCB28122F50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E2D1225-8EA6-4AA5-9838-635D38E04711}"/>
 </file>